--- a/analysis_result.xlsx
+++ b/analysis_result.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Buzón</t>
+          <t>hola</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -593,20 +593,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>50d6a337-b2be-471b-af63-16feb40a1238.wav</t>
+          <t>call-recording.mp3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sin consulta</t>
+          <t>de que trata la llamada</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sí, la llamada trata sobre una oferta de mejora en la promoción de la tarjeta de crédito de BBVA, aunque el cliente no mostró interés en la oferta.</t>
         </is>
       </c>
     </row>
@@ -639,11 +639,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Buzón</t>
+          <t>hola</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
